--- a/E/BIS05D.xlsx
+++ b/E/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="493">
   <si>
     <t/>
   </si>
@@ -253,6 +253,12 @@
     <t>TANGO WFR VANL 95G</t>
   </si>
   <si>
+    <t>20143337</t>
+  </si>
+  <si>
+    <t>TANGO WFLE CHO HZL70</t>
+  </si>
+  <si>
     <t>20138099</t>
   </si>
   <si>
@@ -376,13 +382,13 @@
     <t>20055311</t>
   </si>
   <si>
-    <t>NABATI RCHSE WFR 110</t>
+    <t>NABATI RCHSE WFR 100</t>
   </si>
   <si>
     <t>20055312</t>
   </si>
   <si>
-    <t>NBATI RCHCO WFR C110</t>
+    <t>NBTI RCHCO WFR CK100</t>
   </si>
   <si>
     <t>20138462</t>
@@ -520,15 +526,21 @@
     <t>NYAM2 POPSTIX CHO 48</t>
   </si>
   <si>
+    <t>20134875</t>
+  </si>
+  <si>
+    <t>CHOKI2 STIK CHOCO48G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>10000213</t>
   </si>
   <si>
     <t>GLICO POCKY CHO 47GR</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>10036916</t>
   </si>
   <si>
@@ -697,6 +709,12 @@
     <t>IMPERIAL STRW&amp;CH 100</t>
   </si>
   <si>
+    <t>20125056</t>
+  </si>
+  <si>
+    <t>UNIBIS MRING TART120</t>
+  </si>
+  <si>
     <t>20021257</t>
   </si>
   <si>
@@ -835,6 +853,24 @@
     <t>RT,(E-1.5B)</t>
   </si>
   <si>
+    <t>20143289</t>
+  </si>
+  <si>
+    <t>NSN COOKIES KLPN 60G</t>
+  </si>
+  <si>
+    <t>20143285</t>
+  </si>
+  <si>
+    <t>MONDE SHRTBRD BISC70</t>
+  </si>
+  <si>
+    <t>20143290</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHCLAVA 5</t>
+  </si>
+  <si>
     <t>20133507</t>
   </si>
   <si>
@@ -1202,6 +1238,15 @@
   </si>
   <si>
     <t>37</t>
+  </si>
+  <si>
+    <t>20020089</t>
+  </si>
+  <si>
+    <t>UNIBIS S.H.PUFF 247G</t>
+  </si>
+  <si>
+    <t>,(E-4B)</t>
   </si>
   <si>
     <t>20122975</t>
@@ -1837,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F214"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2561,7 +2606,7 @@
         <v>71</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2581,7 +2626,7 @@
         <v>71</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2601,7 +2646,7 @@
         <v>71</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2609,19 +2654,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2638,10 +2683,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2658,10 +2703,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2678,10 +2723,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2698,10 +2743,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2718,10 +2763,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2729,19 +2774,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2758,10 +2803,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2778,10 +2823,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2798,10 +2843,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2809,19 +2854,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2838,10 +2883,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2858,10 +2903,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2878,10 +2923,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2898,10 +2943,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2909,22 +2954,22 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2938,10 +2983,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>15</v>
@@ -2958,13 +3003,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2978,10 +3023,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2989,19 +3034,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3018,10 +3063,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3038,10 +3083,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3058,10 +3103,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3069,19 +3114,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3098,10 +3143,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3118,10 +3163,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3138,10 +3183,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3158,10 +3203,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3178,10 +3223,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3189,19 +3234,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3218,10 +3263,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3238,13 +3283,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,10 +3303,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>15</v>
@@ -3278,13 +3323,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,10 +3343,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3318,10 +3363,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3338,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3358,13 +3403,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3378,30 +3423,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3418,10 +3463,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3438,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3458,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3478,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3498,10 +3543,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3518,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3538,10 +3583,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3558,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3578,30 +3623,30 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3609,22 +3654,22 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="E89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3658,10 +3703,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3678,10 +3723,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3698,53 +3743,53 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3758,13 +3803,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3778,30 +3823,30 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3809,39 +3854,39 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>220</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3849,39 +3894,39 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3889,36 +3934,36 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>14</v>
@@ -3929,19 +3974,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3949,39 +3994,39 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3989,19 +4034,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4018,10 +4063,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4029,19 +4074,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4049,19 +4094,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4069,19 +4114,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4098,10 +4143,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4118,10 +4163,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4129,19 +4174,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4149,19 +4194,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4169,19 +4214,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4198,10 +4243,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4209,19 +4254,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4229,19 +4274,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4249,19 +4294,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4278,30 +4323,30 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4309,19 +4354,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4329,39 +4374,39 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4369,62 +4414,62 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4438,10 +4483,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4458,30 +4503,30 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>293</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4489,39 +4534,39 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>15</v>
@@ -4529,39 +4574,39 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4569,59 +4614,59 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4629,39 +4674,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4669,19 +4714,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4689,19 +4734,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4709,39 +4754,39 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4749,19 +4794,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4769,39 +4814,39 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4809,19 +4854,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4829,19 +4874,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4849,19 +4894,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4869,19 +4914,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4889,39 +4934,39 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4929,19 +4974,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4949,19 +4994,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4969,19 +5014,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4989,19 +5034,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -5009,19 +5054,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5029,19 +5074,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5049,19 +5094,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5069,19 +5114,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5089,19 +5134,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5109,19 +5154,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5129,19 +5174,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5149,19 +5194,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5169,19 +5214,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5189,19 +5234,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5209,19 +5254,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5229,59 +5274,59 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5289,19 +5334,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5309,19 +5354,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5338,10 +5383,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5358,13 +5403,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5378,213 +5423,213 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>279</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>279</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5598,70 +5643,70 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5678,13 +5723,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5698,10 +5743,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5709,19 +5754,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5729,19 +5774,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5758,10 +5803,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5778,10 +5823,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5798,10 +5843,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5809,39 +5854,39 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5858,10 +5903,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5878,10 +5923,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5898,10 +5943,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5909,19 +5954,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5929,19 +5974,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5958,10 +6003,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5978,10 +6023,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5998,10 +6043,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6018,10 +6063,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6029,19 +6074,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6058,10 +6103,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6078,10 +6123,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6098,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6118,12 +6163,152 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E214" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E215" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="F215" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/BIS05D.xlsx
+++ b/E/BIS05D.xlsx
@@ -19,7 +19,7 @@
     <t>20130350</t>
   </si>
   <si>
-    <t>POCKY CHOCOLATE 154</t>
+    <t>POCKY CHOCOLATE 140</t>
   </si>
   <si>
     <t>BIS05D</t>
@@ -178,7 +178,7 @@
     <t>20132494</t>
   </si>
   <si>
-    <t>LEMONILO BRWNS KJU33</t>
+    <t>LEMONILO BRWNS KJU32</t>
   </si>
   <si>
     <t>7</t>
@@ -187,19 +187,19 @@
     <t>20130152</t>
   </si>
   <si>
-    <t>LEMONILO BROWNIES 33</t>
+    <t>LEMONILO BROWNIES 32</t>
   </si>
   <si>
     <t>20142678</t>
   </si>
   <si>
-    <t>LMNILO LMN CHESSE 33</t>
+    <t>LMNILO LMN CHESSE 32</t>
   </si>
   <si>
     <t>20137230</t>
   </si>
   <si>
-    <t>LEMONILO BRWNS STR33</t>
+    <t>LEMONILO BRWNS STR32</t>
   </si>
   <si>
     <t>20137584</t>
@@ -334,7 +334,7 @@
     <t>20109917</t>
   </si>
   <si>
-    <t>ROMA WFR CHO BLS97.6</t>
+    <t>RMA WAFELO C/BLS97.6</t>
   </si>
   <si>
     <t>20069149</t>
@@ -538,13 +538,13 @@
     <t>10000213</t>
   </si>
   <si>
-    <t>GLICO POCKY CHO 47GR</t>
+    <t>GLICO POCKY CHO 40GR</t>
   </si>
   <si>
     <t>10036916</t>
   </si>
   <si>
-    <t>GLICO POCKY.STRAW 45</t>
+    <t>GLICO POCKY.STRAW39G</t>
   </si>
   <si>
     <t>20086168</t>
@@ -556,7 +556,7 @@
     <t>20138741</t>
   </si>
   <si>
-    <t>GLICO POCKY MILK 39G</t>
+    <t>GLICO POCKY MILK 40G</t>
   </si>
   <si>
     <t>20138740</t>
@@ -568,13 +568,13 @@
     <t>20062839</t>
   </si>
   <si>
-    <t>GLCO POCKY MTCHA 33G</t>
+    <t>GLCO POCKY MTCHA 35G</t>
   </si>
   <si>
     <t>20057865</t>
   </si>
   <si>
-    <t>GLCO POCKY DOU.CHO47</t>
+    <t>GLCO POCKY DOU.CHO39</t>
   </si>
   <si>
     <t>20134839</t>
@@ -1246,7 +1246,7 @@
     <t>UNIBIS S.H.PUFF 247G</t>
   </si>
   <si>
-    <t>,(E-4B)</t>
+    <t>RT,(E-4B)</t>
   </si>
   <si>
     <t>20122975</t>
@@ -1318,7 +1318,7 @@
     <t>10000206</t>
   </si>
   <si>
-    <t>NISSIN CR.CRISPY 250</t>
+    <t>NISSIN CR.CRISPY 225</t>
   </si>
   <si>
     <t>40</t>

--- a/E/BIS05D.xlsx
+++ b/E/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="485">
   <si>
     <t/>
   </si>
@@ -364,12 +364,6 @@
     <t>SPRSTAR TRPL.CHO 6'S</t>
   </si>
   <si>
-    <t>10007336</t>
-  </si>
-  <si>
-    <t>TANGO WFR STRAW 124G</t>
-  </si>
-  <si>
     <t>20027448</t>
   </si>
   <si>
@@ -412,18 +406,6 @@
     <t>BISKUAT BITE CKLT 35</t>
   </si>
   <si>
-    <t>20139060</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE ORI 35G</t>
-  </si>
-  <si>
-    <t>20139686</t>
-  </si>
-  <si>
-    <t>TANGO WFLE WAHH 67.5</t>
-  </si>
-  <si>
     <t>20139392</t>
   </si>
   <si>
@@ -671,12 +653,6 @@
   </si>
   <si>
     <t>19</t>
-  </si>
-  <si>
-    <t>20137568</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.VNL105G</t>
   </si>
   <si>
     <t>20085046</t>
@@ -1882,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F217"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2943,10 +2919,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2954,22 +2930,22 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2983,10 +2959,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>15</v>
@@ -3003,13 +2979,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,10 +2999,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3034,19 +3010,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3063,10 +3039,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3074,19 +3050,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3094,19 +3070,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3114,19 +3090,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3143,10 +3119,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3163,10 +3139,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3183,10 +3159,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3194,19 +3170,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3214,19 +3190,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3234,22 +3210,22 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3263,13 +3239,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,10 +3259,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3303,13 +3279,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,13 +3299,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3343,10 +3319,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3363,13 +3339,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3383,10 +3359,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3394,19 +3370,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3414,39 +3390,39 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3463,10 +3439,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3483,10 +3459,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3503,10 +3479,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3523,10 +3499,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3543,10 +3519,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3563,10 +3539,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3583,10 +3559,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3603,30 +3579,30 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3634,19 +3610,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3654,22 +3630,22 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3683,10 +3659,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3703,10 +3679,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3723,73 +3699,73 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3803,47 +3779,47 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>11</v>
@@ -3854,16 +3830,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>4</v>
@@ -3874,16 +3850,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>14</v>
@@ -3894,59 +3870,59 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>224</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3954,19 +3930,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3974,19 +3950,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3994,39 +3970,39 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -4034,16 +4010,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>4</v>
@@ -4054,16 +4030,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>14</v>
@@ -4074,16 +4050,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
@@ -4094,16 +4070,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>11</v>
@@ -4114,19 +4090,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4143,10 +4119,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4154,19 +4130,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4174,19 +4150,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4194,19 +4170,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4214,16 +4190,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>4</v>
@@ -4234,16 +4210,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>14</v>
@@ -4254,16 +4230,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>8</v>
@@ -4274,16 +4250,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>11</v>
@@ -4294,39 +4270,39 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4334,19 +4310,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4354,19 +4330,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4374,39 +4350,39 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>279</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4414,19 +4390,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4434,19 +4410,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4454,22 +4430,22 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4483,13 +4459,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4503,13 +4479,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4523,10 +4499,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4543,107 +4519,107 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>15</v>
+        <v>297</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>305</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>4</v>
@@ -4654,16 +4630,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>14</v>
@@ -4674,36 +4650,36 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>11</v>
@@ -4714,16 +4690,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
@@ -4734,16 +4710,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>14</v>
@@ -4754,36 +4730,36 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>11</v>
@@ -4794,16 +4770,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>4</v>
@@ -4814,16 +4790,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>14</v>
@@ -4834,16 +4810,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -4854,36 +4830,36 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>4</v>
@@ -4894,16 +4870,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>14</v>
@@ -4914,16 +4890,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>8</v>
@@ -4934,39 +4910,39 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4983,10 +4959,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4994,19 +4970,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -5014,19 +4990,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -5034,19 +5010,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -5054,19 +5030,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5074,19 +5050,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5094,19 +5070,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5114,16 +5090,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>4</v>
@@ -5134,16 +5110,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>14</v>
@@ -5154,16 +5130,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>8</v>
@@ -5174,16 +5150,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>11</v>
@@ -5194,16 +5170,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>4</v>
@@ -5214,16 +5190,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>14</v>
@@ -5234,16 +5210,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>8</v>
@@ -5254,16 +5230,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>11</v>
@@ -5274,16 +5250,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>4</v>
@@ -5294,16 +5270,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>14</v>
@@ -5314,59 +5290,59 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5383,10 +5359,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5403,13 +5379,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5423,13 +5399,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5443,10 +5419,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5463,247 +5439,247 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>403</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B184" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>411</v>
+        <v>191</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>4</v>
@@ -5714,16 +5690,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>14</v>
@@ -5734,16 +5710,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>8</v>
@@ -5754,16 +5730,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>11</v>
@@ -5774,22 +5750,22 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5803,10 +5779,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5814,19 +5790,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5834,19 +5810,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5854,39 +5830,39 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5903,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5914,19 +5890,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5934,16 +5910,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>11</v>
@@ -5954,16 +5930,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>40</v>
@@ -5974,19 +5950,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -6003,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -6014,19 +5990,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -6034,19 +6010,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6054,19 +6030,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6074,19 +6050,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6103,10 +6079,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6123,10 +6099,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6134,19 +6110,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6154,19 +6130,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6174,19 +6150,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6194,19 +6170,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6223,92 +6199,12 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F221" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/BIS05D.xlsx
+++ b/E/BIS05D.xlsx
@@ -295,7 +295,7 @@
     <t>20010655</t>
   </si>
   <si>
-    <t>TANGO WFER CHOCO 240</t>
+    <t>TANGO WFER CHOCO 220</t>
   </si>
   <si>
     <t>10000133</t>
